--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120977982</v>
+        <v>120977980</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>57459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537467</v>
+        <v>537574</v>
       </c>
       <c r="R2" t="n">
-        <v>7200448</v>
+        <v>7200264</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120977980</v>
+        <v>120977982</v>
       </c>
       <c r="B3" t="n">
-        <v>57459</v>
+        <v>78598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537574</v>
+        <v>537467</v>
       </c>
       <c r="R3" t="n">
-        <v>7200264</v>
+        <v>7200448</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120977974</v>
+        <v>120977976</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>78598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,20 +2595,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537561</v>
+        <v>537556</v>
       </c>
       <c r="R19" t="n">
-        <v>7200331</v>
+        <v>7200332</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120977976</v>
+        <v>120977974</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,20 +2707,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537556</v>
+        <v>537561</v>
       </c>
       <c r="R20" t="n">
-        <v>7200332</v>
+        <v>7200331</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120977980</v>
+        <v>120977971</v>
       </c>
       <c r="B2" t="n">
-        <v>57459</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537574</v>
+        <v>537732</v>
       </c>
       <c r="R2" t="n">
-        <v>7200264</v>
+        <v>7200238</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120977982</v>
+        <v>120977984</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537467</v>
+        <v>537515</v>
       </c>
       <c r="R3" t="n">
-        <v>7200448</v>
+        <v>7200610</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +902,7 @@
         <v>120977961</v>
       </c>
       <c r="B4" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120977969</v>
+        <v>120977959</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537720</v>
+        <v>537537</v>
       </c>
       <c r="R5" t="n">
-        <v>7200286</v>
+        <v>7200497</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977959</v>
+        <v>120977975</v>
       </c>
       <c r="B6" t="n">
-        <v>90705</v>
+        <v>79718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537537</v>
+        <v>537562</v>
       </c>
       <c r="R6" t="n">
-        <v>7200497</v>
+        <v>7200330</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120977971</v>
+        <v>120977974</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>79717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,20 +1247,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1279,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537732</v>
+        <v>537561</v>
       </c>
       <c r="R7" t="n">
-        <v>7200238</v>
+        <v>7200331</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120977973</v>
+        <v>120977962</v>
       </c>
       <c r="B8" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537561</v>
+        <v>537628</v>
       </c>
       <c r="R8" t="n">
-        <v>7200332</v>
+        <v>7200394</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977968</v>
+        <v>120977979</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537726</v>
+        <v>537582</v>
       </c>
       <c r="R9" t="n">
-        <v>7200289</v>
+        <v>7200275</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120977966</v>
+        <v>120977964</v>
       </c>
       <c r="B10" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537712</v>
+        <v>537653</v>
       </c>
       <c r="R10" t="n">
-        <v>7200315</v>
+        <v>7200389</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977963</v>
+        <v>120977976</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537653</v>
+        <v>537556</v>
       </c>
       <c r="R11" t="n">
-        <v>7200389</v>
+        <v>7200332</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977970</v>
+        <v>120977967</v>
       </c>
       <c r="B12" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537730</v>
+        <v>537709</v>
       </c>
       <c r="R12" t="n">
-        <v>7200241</v>
+        <v>7200309</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120977981</v>
+        <v>120977982</v>
       </c>
       <c r="B13" t="n">
-        <v>90701</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,7 +1947,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537468</v>
+        <v>537467</v>
       </c>
       <c r="R13" t="n">
         <v>7200448</v>
@@ -2023,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977967</v>
+        <v>120977966</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537709</v>
+        <v>537712</v>
       </c>
       <c r="R14" t="n">
-        <v>7200309</v>
+        <v>7200315</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2135,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120977975</v>
+        <v>120977969</v>
       </c>
       <c r="B15" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537562</v>
+        <v>537720</v>
       </c>
       <c r="R15" t="n">
-        <v>7200330</v>
+        <v>7200286</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120977962</v>
+        <v>120977970</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537628</v>
+        <v>537730</v>
       </c>
       <c r="R16" t="n">
-        <v>7200394</v>
+        <v>7200241</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977977</v>
+        <v>120977980</v>
       </c>
       <c r="B17" t="n">
-        <v>79715</v>
+        <v>57462</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,34 +2371,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537561</v>
+        <v>537574</v>
       </c>
       <c r="R17" t="n">
-        <v>7200345</v>
+        <v>7200264</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120977984</v>
+        <v>120977973</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>79683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537515</v>
+        <v>537561</v>
       </c>
       <c r="R18" t="n">
-        <v>7200610</v>
+        <v>7200332</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120977976</v>
+        <v>120977981</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537556</v>
+        <v>537468</v>
       </c>
       <c r="R19" t="n">
-        <v>7200332</v>
+        <v>7200448</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120977974</v>
+        <v>120977983</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537561</v>
+        <v>537514</v>
       </c>
       <c r="R20" t="n">
-        <v>7200331</v>
+        <v>7200604</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120977978</v>
+        <v>120977963</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537579</v>
+        <v>537653</v>
       </c>
       <c r="R21" t="n">
-        <v>7200272</v>
+        <v>7200389</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120977983</v>
+        <v>120977978</v>
       </c>
       <c r="B22" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537514</v>
+        <v>537579</v>
       </c>
       <c r="R22" t="n">
-        <v>7200604</v>
+        <v>7200272</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120977960</v>
+        <v>120977968</v>
       </c>
       <c r="B23" t="n">
-        <v>57501</v>
+        <v>90715</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,38 +3047,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537541</v>
+        <v>537726</v>
       </c>
       <c r="R23" t="n">
-        <v>7200485</v>
+        <v>7200289</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3110,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3120,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120977979</v>
+        <v>120977977</v>
       </c>
       <c r="B24" t="n">
-        <v>90687</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,25 +3155,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537582</v>
+        <v>537561</v>
       </c>
       <c r="R24" t="n">
-        <v>7200275</v>
+        <v>7200345</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120977964</v>
+        <v>120977960</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3275,34 +3271,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537653</v>
+        <v>537541</v>
       </c>
       <c r="R25" t="n">
-        <v>7200389</v>
+        <v>7200485</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120977982</v>
+        <v>120977980</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,38 +1919,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537467</v>
+        <v>537574</v>
       </c>
       <c r="R13" t="n">
-        <v>7200448</v>
+        <v>7200264</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977966</v>
+        <v>120977982</v>
       </c>
       <c r="B14" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2035,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537712</v>
+        <v>537467</v>
       </c>
       <c r="R14" t="n">
-        <v>7200315</v>
+        <v>7200448</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120977969</v>
+        <v>120977966</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2147,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537720</v>
+        <v>537712</v>
       </c>
       <c r="R15" t="n">
-        <v>7200286</v>
+        <v>7200315</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120977970</v>
+        <v>120977969</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537730</v>
+        <v>537720</v>
       </c>
       <c r="R16" t="n">
-        <v>7200241</v>
+        <v>7200286</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977980</v>
+        <v>120977970</v>
       </c>
       <c r="B17" t="n">
-        <v>57462</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,42 +2371,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537574</v>
+        <v>537730</v>
       </c>
       <c r="R17" t="n">
-        <v>7200264</v>
+        <v>7200241</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120977977</v>
+        <v>120977960</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>57504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,38 +3155,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537561</v>
+        <v>537541</v>
       </c>
       <c r="R24" t="n">
-        <v>7200345</v>
+        <v>7200485</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3218,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120977960</v>
+        <v>120977977</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>79718</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,42 +3271,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537541</v>
+        <v>537561</v>
       </c>
       <c r="R25" t="n">
-        <v>7200485</v>
+        <v>7200345</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -3143,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120977960</v>
+        <v>120977977</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
+        <v>79718</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,42 +3155,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537541</v>
+        <v>537561</v>
       </c>
       <c r="R24" t="n">
-        <v>7200485</v>
+        <v>7200345</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120977977</v>
+        <v>120977960</v>
       </c>
       <c r="B25" t="n">
-        <v>79718</v>
+        <v>57504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,38 +3267,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537561</v>
+        <v>537541</v>
       </c>
       <c r="R25" t="n">
-        <v>7200345</v>
+        <v>7200485</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120977971</v>
+        <v>120977964</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537732</v>
+        <v>537653</v>
       </c>
       <c r="R2" t="n">
-        <v>7200238</v>
+        <v>7200389</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120977984</v>
+        <v>120977969</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537515</v>
+        <v>537720</v>
       </c>
       <c r="R3" t="n">
-        <v>7200610</v>
+        <v>7200286</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120977961</v>
+        <v>120977959</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537629</v>
+        <v>537537</v>
       </c>
       <c r="R4" t="n">
-        <v>7200392</v>
+        <v>7200497</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120977959</v>
+        <v>120977982</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537537</v>
+        <v>537467</v>
       </c>
       <c r="R5" t="n">
-        <v>7200497</v>
+        <v>7200448</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977975</v>
+        <v>120977977</v>
       </c>
       <c r="B6" t="n">
         <v>79718</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537562</v>
+        <v>537561</v>
       </c>
       <c r="R6" t="n">
-        <v>7200330</v>
+        <v>7200345</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120977974</v>
+        <v>120977979</v>
       </c>
       <c r="B7" t="n">
-        <v>79717</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537561</v>
+        <v>537582</v>
       </c>
       <c r="R7" t="n">
-        <v>7200331</v>
+        <v>7200275</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120977962</v>
+        <v>120977975</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537628</v>
+        <v>537562</v>
       </c>
       <c r="R8" t="n">
-        <v>7200394</v>
+        <v>7200330</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977979</v>
+        <v>120977983</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537582</v>
+        <v>537514</v>
       </c>
       <c r="R9" t="n">
-        <v>7200275</v>
+        <v>7200604</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120977964</v>
+        <v>120977981</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90711</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537653</v>
+        <v>537468</v>
       </c>
       <c r="R10" t="n">
-        <v>7200389</v>
+        <v>7200448</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977976</v>
+        <v>120977973</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537556</v>
+        <v>537561</v>
       </c>
       <c r="R11" t="n">
         <v>7200332</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977967</v>
+        <v>120977962</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537709</v>
+        <v>537628</v>
       </c>
       <c r="R12" t="n">
-        <v>7200309</v>
+        <v>7200394</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120977980</v>
+        <v>120977976</v>
       </c>
       <c r="B13" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,42 +1919,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537574</v>
+        <v>537556</v>
       </c>
       <c r="R13" t="n">
-        <v>7200264</v>
+        <v>7200332</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977982</v>
+        <v>120977963</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537467</v>
+        <v>537653</v>
       </c>
       <c r="R14" t="n">
-        <v>7200448</v>
+        <v>7200389</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120977966</v>
+        <v>120977970</v>
       </c>
       <c r="B15" t="n">
-        <v>79718</v>
+        <v>90693</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537712</v>
+        <v>537730</v>
       </c>
       <c r="R15" t="n">
-        <v>7200315</v>
+        <v>7200241</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120977969</v>
+        <v>120977967</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2287,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537720</v>
+        <v>537709</v>
       </c>
       <c r="R16" t="n">
-        <v>7200286</v>
+        <v>7200309</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977970</v>
+        <v>120977971</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537730</v>
+        <v>537732</v>
       </c>
       <c r="R17" t="n">
-        <v>7200241</v>
+        <v>7200238</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120977973</v>
+        <v>120977960</v>
       </c>
       <c r="B18" t="n">
-        <v>79683</v>
+        <v>57504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,34 +2483,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537561</v>
+        <v>537541</v>
       </c>
       <c r="R18" t="n">
-        <v>7200332</v>
+        <v>7200485</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120977981</v>
+        <v>120977968</v>
       </c>
       <c r="B19" t="n">
-        <v>90711</v>
+        <v>90715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537468</v>
+        <v>537726</v>
       </c>
       <c r="R19" t="n">
-        <v>7200448</v>
+        <v>7200289</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120977983</v>
+        <v>120977978</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537514</v>
+        <v>537579</v>
       </c>
       <c r="R20" t="n">
-        <v>7200604</v>
+        <v>7200272</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120977963</v>
+        <v>120977974</v>
       </c>
       <c r="B21" t="n">
-        <v>79711</v>
+        <v>79717</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,21 +2823,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537653</v>
+        <v>537561</v>
       </c>
       <c r="R21" t="n">
-        <v>7200389</v>
+        <v>7200331</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120977978</v>
+        <v>120977984</v>
       </c>
       <c r="B22" t="n">
         <v>78601</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537579</v>
+        <v>537515</v>
       </c>
       <c r="R22" t="n">
-        <v>7200272</v>
+        <v>7200610</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120977968</v>
+        <v>120977961</v>
       </c>
       <c r="B23" t="n">
-        <v>90715</v>
+        <v>82385</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537726</v>
+        <v>537629</v>
       </c>
       <c r="R23" t="n">
-        <v>7200289</v>
+        <v>7200392</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,7 +3143,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120977977</v>
+        <v>120977966</v>
       </c>
       <c r="B24" t="n">
         <v>79718</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537561</v>
+        <v>537712</v>
       </c>
       <c r="R24" t="n">
-        <v>7200345</v>
+        <v>7200315</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120977960</v>
+        <v>120977980</v>
       </c>
       <c r="B25" t="n">
-        <v>57504</v>
+        <v>57462</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,30 +3267,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537541</v>
+        <v>537574</v>
       </c>
       <c r="R25" t="n">
-        <v>7200485</v>
+        <v>7200264</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977973</v>
+        <v>120977962</v>
       </c>
       <c r="B11" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537561</v>
+        <v>537628</v>
       </c>
       <c r="R11" t="n">
-        <v>7200332</v>
+        <v>7200394</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977962</v>
+        <v>120977976</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537628</v>
+        <v>537556</v>
       </c>
       <c r="R12" t="n">
-        <v>7200394</v>
+        <v>7200332</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120977976</v>
+        <v>120977963</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537556</v>
+        <v>537653</v>
       </c>
       <c r="R13" t="n">
-        <v>7200332</v>
+        <v>7200389</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977963</v>
+        <v>120977973</v>
       </c>
       <c r="B14" t="n">
-        <v>79711</v>
+        <v>79683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537653</v>
+        <v>537561</v>
       </c>
       <c r="R14" t="n">
-        <v>7200389</v>
+        <v>7200332</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40984-2024 artfynd.xlsx
+++ b/artfynd/A 40984-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120977964</v>
+        <v>120977962</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537653</v>
+        <v>537628</v>
       </c>
       <c r="R2" t="n">
-        <v>7200389</v>
+        <v>7200394</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120977969</v>
+        <v>120977967</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537720</v>
+        <v>537709</v>
       </c>
       <c r="R3" t="n">
-        <v>7200286</v>
+        <v>7200309</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120977959</v>
+        <v>120977973</v>
       </c>
       <c r="B4" t="n">
-        <v>90715</v>
+        <v>79686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537537</v>
+        <v>537561</v>
       </c>
       <c r="R4" t="n">
-        <v>7200497</v>
+        <v>7200332</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120977982</v>
+        <v>120977966</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>79721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537467</v>
+        <v>537712</v>
       </c>
       <c r="R5" t="n">
-        <v>7200448</v>
+        <v>7200315</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120977977</v>
+        <v>120977978</v>
       </c>
       <c r="B6" t="n">
-        <v>79718</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537561</v>
+        <v>537579</v>
       </c>
       <c r="R6" t="n">
-        <v>7200345</v>
+        <v>7200272</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120977979</v>
+        <v>120977959</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537582</v>
+        <v>537537</v>
       </c>
       <c r="R7" t="n">
-        <v>7200275</v>
+        <v>7200497</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120977975</v>
+        <v>120977980</v>
       </c>
       <c r="B8" t="n">
-        <v>79718</v>
+        <v>57462</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537562</v>
+        <v>537574</v>
       </c>
       <c r="R8" t="n">
-        <v>7200330</v>
+        <v>7200264</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977983</v>
+        <v>120977981</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>90723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537514</v>
+        <v>537468</v>
       </c>
       <c r="R9" t="n">
-        <v>7200604</v>
+        <v>7200448</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120977981</v>
+        <v>120977971</v>
       </c>
       <c r="B10" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537468</v>
+        <v>537732</v>
       </c>
       <c r="R10" t="n">
-        <v>7200448</v>
+        <v>7200238</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977962</v>
+        <v>120977968</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537628</v>
+        <v>537726</v>
       </c>
       <c r="R11" t="n">
-        <v>7200394</v>
+        <v>7200289</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977976</v>
+        <v>120977960</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1815,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537556</v>
+        <v>537541</v>
       </c>
       <c r="R12" t="n">
-        <v>7200332</v>
+        <v>7200485</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120977963</v>
+        <v>120977982</v>
       </c>
       <c r="B13" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1927,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537653</v>
+        <v>537467</v>
       </c>
       <c r="R13" t="n">
-        <v>7200389</v>
+        <v>7200448</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120977973</v>
+        <v>120977969</v>
       </c>
       <c r="B14" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2043,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537561</v>
+        <v>537720</v>
       </c>
       <c r="R14" t="n">
-        <v>7200332</v>
+        <v>7200286</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120977970</v>
+        <v>120977963</v>
       </c>
       <c r="B15" t="n">
-        <v>90693</v>
+        <v>79714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537730</v>
+        <v>537653</v>
       </c>
       <c r="R15" t="n">
-        <v>7200241</v>
+        <v>7200389</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120977967</v>
+        <v>120977984</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537709</v>
+        <v>537515</v>
       </c>
       <c r="R16" t="n">
-        <v>7200309</v>
+        <v>7200610</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120977971</v>
+        <v>120977979</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2379,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537732</v>
+        <v>537582</v>
       </c>
       <c r="R17" t="n">
-        <v>7200238</v>
+        <v>7200275</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2475,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120977960</v>
+        <v>120977974</v>
       </c>
       <c r="B18" t="n">
-        <v>57504</v>
+        <v>79720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,42 +2487,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537541</v>
+        <v>537561</v>
       </c>
       <c r="R18" t="n">
-        <v>7200485</v>
+        <v>7200331</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2560,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120977968</v>
+        <v>120977964</v>
       </c>
       <c r="B19" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2603,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537726</v>
+        <v>537653</v>
       </c>
       <c r="R19" t="n">
-        <v>7200289</v>
+        <v>7200389</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2662,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2672,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120977978</v>
+        <v>120977961</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537579</v>
+        <v>537629</v>
       </c>
       <c r="R20" t="n">
-        <v>7200272</v>
+        <v>7200392</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120977974</v>
+        <v>120977983</v>
       </c>
       <c r="B21" t="n">
-        <v>79717</v>
+        <v>90705</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,25 +2823,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537561</v>
+        <v>537514</v>
       </c>
       <c r="R21" t="n">
-        <v>7200331</v>
+        <v>7200604</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2886,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2896,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2923,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120977984</v>
+        <v>120977970</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,21 +2939,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537515</v>
+        <v>537730</v>
       </c>
       <c r="R22" t="n">
-        <v>7200610</v>
+        <v>7200241</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3008,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120977961</v>
+        <v>120977976</v>
       </c>
       <c r="B23" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,21 +3051,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537629</v>
+        <v>537556</v>
       </c>
       <c r="R23" t="n">
-        <v>7200392</v>
+        <v>7200332</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3120,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120977966</v>
+        <v>120977977</v>
       </c>
       <c r="B24" t="n">
-        <v>79718</v>
+        <v>79721</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3183,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537712</v>
+        <v>537561</v>
       </c>
       <c r="R24" t="n">
-        <v>7200315</v>
+        <v>7200345</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3218,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120977980</v>
+        <v>120977975</v>
       </c>
       <c r="B25" t="n">
-        <v>57462</v>
+        <v>79721</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3271,38 +3275,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537574</v>
+        <v>537562</v>
       </c>
       <c r="R25" t="n">
-        <v>7200264</v>
+        <v>7200330</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
